--- a/output/mf_ranked_hybrid.xlsx
+++ b/output/mf_ranked_hybrid.xlsx
@@ -17024,7 +17024,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-21 20:48:45 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
+          <t>Generated: 2026-08-29 02:52:29 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
         </is>
       </c>
     </row>

--- a/output/mf_ranked_hybrid.xlsx
+++ b/output/mf_ranked_hybrid.xlsx
@@ -17024,7 +17024,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-29 02:52:29 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
+          <t>Generated: 2026-09-04 22:26:37 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
         </is>
       </c>
     </row>

--- a/output/mf_ranked_hybrid.xlsx
+++ b/output/mf_ranked_hybrid.xlsx
@@ -17024,7 +17024,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-04 22:26:37 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
+          <t>Generated: 2026-09-11 22:42:48 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
         </is>
       </c>
     </row>

--- a/output/mf_ranked_hybrid.xlsx
+++ b/output/mf_ranked_hybrid.xlsx
@@ -17024,7 +17024,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-11 22:42:48 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
+          <t>Generated: 2026-09-18 22:43:30 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
         </is>
       </c>
     </row>

--- a/output/mf_ranked_hybrid.xlsx
+++ b/output/mf_ranked_hybrid.xlsx
@@ -17024,7 +17024,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-18 22:43:30 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
+          <t>Generated: 2026-09-25 23:23:22 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
         </is>
       </c>
     </row>

--- a/output/mf_ranked_hybrid.xlsx
+++ b/output/mf_ranked_hybrid.xlsx
@@ -17024,7 +17024,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-25 23:23:22 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
+          <t>Generated: 2026-10-02 23:55:34 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
         </is>
       </c>
     </row>

--- a/output/mf_ranked_hybrid.xlsx
+++ b/output/mf_ranked_hybrid.xlsx
@@ -17024,7 +17024,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-02 23:55:34 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
+          <t>Generated: 2026-10-10 00:11:54 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
         </is>
       </c>
     </row>

--- a/output/mf_ranked_hybrid.xlsx
+++ b/output/mf_ranked_hybrid.xlsx
@@ -17024,7 +17024,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-10 00:11:54 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
+          <t>Generated: 2026-10-16 22:56:14 | Comprehensive Documentation | All Values Numeric (0 = Missing)</t>
         </is>
       </c>
     </row>
